--- a/CC2022 analysis/CC2022 SFRs and SARs v2.xlsx
+++ b/CC2022 analysis/CC2022 SFRs and SARs v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oracle-my.sharepoint.com/personal/maureen_barry_oracle_com/Documents/Maureens files/Common Criteria/PPs/DBMS/Supporting docs/cPP/CC2022 work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="175" documentId="8_{02C5BEF3-B7A1-44A7-9617-A7839DC6A302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7A66A3D-FC34-44B2-BFF3-CCA614E7AE12}"/>
+  <xr:revisionPtr revIDLastSave="178" documentId="8_{02C5BEF3-B7A1-44A7-9617-A7839DC6A302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C7B968F-00ED-4DD4-851C-30D4F4578A6E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SFRs" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="102">
   <si>
     <t>FAU_GEN.1.1</t>
   </si>
@@ -619,9 +619,6 @@
   </si>
   <si>
     <t>no change to cPP or SD</t>
-  </si>
-  <si>
-    <t>Review as a group SD section 4.6 Vulnerability Analysis (AVA_VAN.2)</t>
   </si>
   <si>
     <t>APE_CCL.1</t>
@@ -1068,6 +1065,9 @@
   </si>
   <si>
     <t>reviewed as a team - applicable to ST writer…not PP writer</t>
+  </si>
+  <si>
+    <t>Reviewed SD section 4.6 Vulnerability Analysis (AVA_VAN.2) to confirm that there are no changes to CEM activities between 3.1.5 and CC:2022</t>
   </si>
 </sst>
 </file>
@@ -1133,13 +1133,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="3" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.39997558519241921"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1174,17 +1174,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1194,6 +1191,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1795,117 +1795,117 @@
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
       <c r="F4" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="30" x14ac:dyDescent="0.25">
       <c r="F5" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>81</v>
+        <v>78</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="30" x14ac:dyDescent="0.25">
       <c r="F6" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="G6" s="17"/>
+        <v>79</v>
+      </c>
+      <c r="G6" s="16"/>
     </row>
     <row r="7" spans="2:8" ht="30" x14ac:dyDescent="0.25">
       <c r="F7" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="G7" s="17"/>
+        <v>77</v>
+      </c>
+      <c r="G7" s="16"/>
     </row>
     <row r="8" spans="2:8" ht="30" x14ac:dyDescent="0.25">
       <c r="F8" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="G8" s="17"/>
+        <v>81</v>
+      </c>
+      <c r="G8" s="16"/>
     </row>
     <row r="9" spans="2:8" ht="30" x14ac:dyDescent="0.25">
       <c r="F9" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="G9" s="17"/>
+        <v>82</v>
+      </c>
+      <c r="G9" s="16"/>
     </row>
     <row r="10" spans="2:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10" s="16" t="s">
         <v>84</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="30" x14ac:dyDescent="0.25">
       <c r="F11" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="G11" s="17"/>
+        <v>85</v>
+      </c>
+      <c r="G11" s="16"/>
     </row>
     <row r="12" spans="2:8" ht="30" x14ac:dyDescent="0.25">
       <c r="F12" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="G12" s="15" t="s">
-        <v>88</v>
-      </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="F13" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="G13" s="15"/>
+      <c r="F13" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="G13" s="14"/>
     </row>
     <row r="14" spans="2:8" ht="45" x14ac:dyDescent="0.25">
       <c r="F14" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" s="16" t="s">
         <v>89</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="45" x14ac:dyDescent="0.25">
       <c r="F15" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G15" s="17"/>
+        <v>90</v>
+      </c>
+      <c r="G15" s="16"/>
     </row>
     <row r="16" spans="2:8" ht="45" x14ac:dyDescent="0.25">
       <c r="F16" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="G16" s="17"/>
+        <v>99</v>
+      </c>
+      <c r="G16" s="16"/>
     </row>
     <row r="17" spans="6:7" ht="30" x14ac:dyDescent="0.25">
       <c r="F17" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="G17" s="14" t="s">
         <v>92</v>
-      </c>
-      <c r="G17" s="15" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="18" spans="6:7" ht="45" x14ac:dyDescent="0.25">
       <c r="F18" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="G18" s="16" t="s">
         <v>94</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="19" spans="6:7" ht="75" x14ac:dyDescent="0.25">
       <c r="F19" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G19" s="17"/>
+        <v>95</v>
+      </c>
+      <c r="G19" s="16"/>
     </row>
     <row r="20" spans="6:7" ht="150" x14ac:dyDescent="0.25">
       <c r="F20" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="G20" s="15" t="s">
         <v>97</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2008,11 +2008,14 @@
       <c r="B13" s="4"/>
       <c r="F13" s="4"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="14" t="s">
-        <v>75</v>
+    <row r="14" spans="2:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="B14" s="17" t="s">
+        <v>101</v>
       </c>
       <c r="F14" s="2"/>
+      <c r="G14" t="s">
+        <v>74</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2084,7 +2087,7 @@
       <c r="F8" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="16" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2092,26 +2095,26 @@
       <c r="F9" t="s">
         <v>54</v>
       </c>
-      <c r="G9" s="17"/>
+      <c r="G9" s="16"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="F10" t="s">
         <v>73</v>
       </c>
-      <c r="G10" s="17"/>
+      <c r="G10" s="16"/>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="F11" t="s">
         <v>56</v>
       </c>
-      <c r="G11" s="17"/>
+      <c r="G11" s="16"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="F12" t="s">
         <v>57</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="60" x14ac:dyDescent="0.25">
@@ -2136,7 +2139,7 @@
         <v>62</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
@@ -2158,7 +2161,7 @@
         <v>65</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -2177,7 +2180,7 @@
         <v>69</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
